--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -638,7 +638,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -928,6 +928,14 @@
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP7796-8"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.category:second.id</t>
   </si>
   <si>
@@ -944,9 +952,6 @@
   </si>
   <si>
     <t>Observation.category:second.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.category:second.coding.version</t>
@@ -4608,7 +4613,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -5373,7 +5378,7 @@
         <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>83</v>
@@ -5447,7 +5452,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>210</v>
@@ -5565,7 +5570,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>217</v>
@@ -5685,7 +5690,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>223</v>
@@ -5807,7 +5812,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>233</v>
@@ -5925,7 +5930,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>235</v>
@@ -6045,7 +6050,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>237</v>
@@ -6056,7 +6061,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>
@@ -6090,7 +6095,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="538">
   <si>
     <t>Property</t>
   </si>
@@ -666,6 +666,14 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="procedure"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -820,9 +828,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>procedure</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -960,9 +965,6 @@
     <t>Observation.category:second.coding.code</t>
   </si>
   <si>
-    <t>LP7796-8</t>
-  </si>
-  <si>
     <t>Observation.category:second.coding.display</t>
   </si>
   <si>
@@ -1022,7 +1024,7 @@
     <t>このObservationの対象となる患者や患者群、機器、場所に関する情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
+    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
@@ -1383,7 +1385,7 @@
     <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
   </si>
   <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
+    <t>これは、結果の送信に関与する機器（ゲートウェイなど）を表すことを意図したものではない。そのような機器は、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -3932,7 +3934,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3951,7 +3953,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4004,10 +4006,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4030,13 +4032,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4087,7 +4089,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4111,7 +4113,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4122,10 +4124,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4154,7 +4156,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4195,10 +4197,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4207,7 +4209,7 @@
         <v>200</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4231,7 +4233,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4242,10 +4244,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4268,19 +4270,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4329,7 +4331,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4350,10 +4352,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4364,10 +4366,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4390,13 +4392,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4447,7 +4449,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4471,7 +4473,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4482,10 +4484,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4514,7 +4516,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4555,10 +4557,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -4567,7 +4569,7 @@
         <v>200</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4591,7 +4593,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4602,10 +4604,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4631,23 +4633,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4689,7 +4691,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4710,10 +4712,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4724,10 +4726,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4750,16 +4752,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4809,7 +4811,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4830,10 +4832,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4844,10 +4846,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4873,21 +4875,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>259</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4990,7 +4992,7 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>265</v>
@@ -5232,7 +5234,7 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>283</v>
@@ -5455,7 +5457,7 @@
         <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5478,13 +5480,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5535,7 +5537,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5559,7 +5561,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5573,7 +5575,7 @@
         <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5602,7 +5604,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5643,10 +5645,10 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
@@ -5655,7 +5657,7 @@
         <v>200</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5679,7 +5681,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5693,7 +5695,7 @@
         <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5716,19 +5718,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5777,7 +5779,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5798,10 +5800,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5815,7 +5817,7 @@
         <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5838,13 +5840,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5895,7 +5897,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5919,7 +5921,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5933,7 +5935,7 @@
         <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5962,7 +5964,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6003,10 +6005,10 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
@@ -6015,7 +6017,7 @@
         <v>200</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6039,7 +6041,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6053,7 +6055,7 @@
         <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6079,16 +6081,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6137,7 +6139,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6158,10 +6160,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6175,7 +6177,7 @@
         <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6198,16 +6200,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6257,7 +6259,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6278,10 +6280,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6295,7 +6297,7 @@
         <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6321,21 +6323,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>303</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6412,7 +6414,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>264</v>
@@ -6438,7 +6440,7 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>265</v>
@@ -6532,7 +6534,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>272</v>
@@ -6654,7 +6656,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>282</v>
@@ -6680,7 +6682,7 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>283</v>
@@ -6776,14 +6778,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6805,16 +6807,16 @@
         <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6843,7 +6845,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6861,7 +6863,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -6876,30 +6878,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6922,19 +6924,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6983,7 +6985,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6998,19 +7000,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7018,10 +7020,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7044,16 +7046,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7103,7 +7105,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7124,13 +7126,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7138,14 +7140,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7164,19 +7166,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7225,7 +7227,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7240,19 +7242,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7260,14 +7262,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7286,19 +7288,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7347,7 +7349,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7362,19 +7364,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7382,10 +7384,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7408,16 +7410,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7467,7 +7469,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7488,13 +7490,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7502,10 +7504,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7528,19 +7530,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7589,7 +7591,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7604,19 +7606,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AL46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7624,10 +7626,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7653,16 +7655,16 @@
         <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7687,11 +7689,11 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7709,7 +7711,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7718,7 +7720,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7727,27 +7729,27 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7773,16 +7775,16 @@
         <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7807,14 +7809,14 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Z48" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>389</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7831,7 +7833,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7840,7 +7842,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7855,7 +7857,7 @@
         <v>137</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7866,14 +7868,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7895,16 +7897,16 @@
         <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7929,14 +7931,14 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7953,7 +7955,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7971,27 +7973,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>402</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8014,19 +8016,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8075,7 +8077,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8096,10 +8098,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8110,10 +8112,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8139,13 +8141,13 @@
         <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8171,14 +8173,14 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8195,7 +8197,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8213,27 +8215,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>418</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8259,16 +8261,16 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8293,14 +8295,14 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8317,7 +8319,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8338,10 +8340,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8352,10 +8354,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8378,16 +8380,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8437,7 +8439,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8455,27 +8457,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>434</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8498,16 +8500,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8557,7 +8559,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8575,27 +8577,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>442</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8618,19 +8620,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8679,7 +8681,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8691,19 +8693,19 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8714,10 +8716,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8740,13 +8742,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8797,7 +8799,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8821,7 +8823,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8832,10 +8834,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8864,7 +8866,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -8917,7 +8919,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8941,7 +8943,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8952,14 +8954,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8981,10 +8983,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9039,7 +9041,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9074,10 +9076,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9100,13 +9102,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9157,7 +9159,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9166,7 +9168,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9178,10 +9180,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9192,10 +9194,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9218,13 +9220,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9275,7 +9277,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9284,7 +9286,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9296,10 +9298,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9310,10 +9312,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9339,16 +9341,16 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9376,11 +9378,11 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>474</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9397,7 +9399,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9415,13 +9417,13 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AM61" t="s" s="2">
-        <v>476</v>
-      </c>
       <c r="AN61" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9432,10 +9434,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9461,16 +9463,16 @@
         <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9495,14 +9497,14 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>483</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9519,7 +9521,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9537,13 +9539,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AM62" t="s" s="2">
-        <v>476</v>
-      </c>
       <c r="AN62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9554,10 +9556,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9580,17 +9582,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L63" t="s" s="2">
-        <v>486</v>
-      </c>
       <c r="M63" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9639,7 +9641,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9663,7 +9665,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9674,10 +9676,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9700,13 +9702,13 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9757,7 +9759,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9778,10 +9780,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9792,10 +9794,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9818,16 +9820,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9877,7 +9879,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9898,10 +9900,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9912,10 +9914,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9938,16 +9940,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9997,7 +9999,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10018,10 +10020,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10032,10 +10034,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10058,19 +10060,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10119,7 +10121,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10140,10 +10142,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10154,10 +10156,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10180,13 +10182,13 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10237,7 +10239,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10261,7 +10263,7 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10272,10 +10274,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10304,7 +10306,7 @@
         <v>141</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>143</v>
@@ -10357,7 +10359,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10381,7 +10383,7 @@
         <v>83</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10392,14 +10394,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10421,10 +10423,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10479,7 +10481,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10514,10 +10516,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10543,16 +10545,16 @@
         <v>192</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="N71" t="s" s="2">
-        <v>516</v>
-      </c>
       <c r="O71" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10577,14 +10579,14 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>518</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10601,7 +10603,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10619,16 +10621,16 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AN71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -10636,10 +10638,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10662,19 +10664,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N72" t="s" s="2">
-        <v>524</v>
-      </c>
       <c r="O72" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10723,7 +10725,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10741,27 +10743,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10787,16 +10789,16 @@
         <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="N73" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="O73" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10821,14 +10823,14 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="Y73" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Y73" t="s" s="2">
+      <c r="Z73" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>389</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
       </c>
@@ -10845,7 +10847,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10854,7 +10856,7 @@
         <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>106</v>
@@ -10869,7 +10871,7 @@
         <v>137</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10880,14 +10882,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10909,16 +10911,16 @@
         <v>192</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10943,14 +10945,14 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
       </c>
@@ -10967,7 +10969,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10985,27 +10987,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>402</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11031,16 +11033,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11089,7 +11091,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11110,10 +11112,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
